--- a/exports/trend_1d/PATANJALI_full_report.xlsx
+++ b/exports/trend_1d/PATANJALI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:U47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.09</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43971</v>
+        <v>43972</v>
       </c>
       <c r="H2" t="n">
-        <v>212.7</v>
+        <v>202.1</v>
       </c>
       <c r="I2" t="n">
         <v>212.0652461654462</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K2" t="n">
-        <v>2115.62</v>
+        <v>2005.21</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>14.38</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H3" t="n">
-        <v>200.6</v>
+        <v>210.6</v>
       </c>
       <c r="I3" t="n">
         <v>202.2693036125891</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>0.74</v>
+        <v>-4.21</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="M3" t="n">
-        <v>4.87</v>
+        <v>4.99</v>
       </c>
       <c r="N3" t="n">
         <v>5.03</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>15.66</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44012</v>
+        <v>44013</v>
       </c>
       <c r="H4" t="n">
-        <v>457.2</v>
+        <v>434.3</v>
       </c>
       <c r="I4" t="n">
         <v>448.5333089055408</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" t="n">
-        <v>117.09</v>
+        <v>106.22</v>
       </c>
       <c r="L4" t="n">
         <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>4.99</v>
+        <v>5.01</v>
       </c>
       <c r="N4" t="n">
         <v>5.01</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>14.22</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44103</v>
+        <v>44104</v>
       </c>
       <c r="H5" t="n">
-        <v>164</v>
+        <v>172.2</v>
       </c>
       <c r="I5" t="n">
         <v>169.1531903484984</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="n">
-        <v>62.24</v>
+        <v>60.35</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>17.8</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44117</v>
+        <v>44118</v>
       </c>
       <c r="H6" t="n">
-        <v>185.6</v>
+        <v>179.2</v>
       </c>
       <c r="I6" t="n">
         <v>181.8461890175829</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>7.78</v>
+        <v>4.07</v>
       </c>
       <c r="L6" t="n">
         <v>4.18</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>20.53</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44152</v>
+        <v>44153</v>
       </c>
       <c r="H7" t="n">
-        <v>187.3</v>
+        <v>196.6</v>
       </c>
       <c r="I7" t="n">
         <v>194.8899475074762</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.52</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>5.3</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>4.99</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.45</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44208</v>
+        <v>44209</v>
       </c>
       <c r="H8" t="n">
-        <v>220</v>
+        <v>216.8</v>
       </c>
       <c r="I8" t="n">
         <v>219.0245614376122</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K8" t="n">
-        <v>11.9</v>
+        <v>10.27</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>11.19</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44229</v>
+        <v>44230</v>
       </c>
       <c r="H9" t="n">
-        <v>212.7</v>
+        <v>223.4</v>
       </c>
       <c r="I9" t="n">
         <v>216.4775171836177</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>1.89</v>
+        <v>-3.04</v>
       </c>
       <c r="L9" t="n">
-        <v>2.31</v>
+        <v>3.04</v>
       </c>
       <c r="M9" t="n">
-        <v>2.84</v>
+        <v>5.03</v>
       </c>
       <c r="N9" t="n">
-        <v>4.99</v>
+        <v>5.03</v>
       </c>
       <c r="O9" t="n">
         <v>-1.45</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.11</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H10" t="n">
-        <v>230</v>
+        <v>224.9</v>
       </c>
       <c r="I10" t="n">
         <v>226.1876384222742</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" t="n">
-        <v>2.95</v>
+        <v>0.67</v>
       </c>
       <c r="L10" t="n">
         <v>2.42</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>12.01</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H11" t="n">
-        <v>225.1</v>
+        <v>245.2</v>
       </c>
       <c r="I11" t="n">
         <v>239.1912498182767</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.09</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>9.380000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="M11" t="n">
         <v>3.73</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.97</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44371</v>
+        <v>44372</v>
       </c>
       <c r="H12" t="n">
-        <v>374.4</v>
+        <v>360.8</v>
       </c>
       <c r="I12" t="n">
         <v>374.0759915938114</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K12" t="n">
-        <v>52.69</v>
+        <v>47.15</v>
       </c>
       <c r="L12" t="n">
         <v>7.95</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>17.14</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44509</v>
+        <v>44510</v>
       </c>
       <c r="H13" t="n">
-        <v>321.9</v>
+        <v>343.6</v>
       </c>
       <c r="I13" t="n">
         <v>324.3755504066039</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K13" t="n">
-        <v>10.78</v>
+        <v>4.77</v>
       </c>
       <c r="L13" t="n">
         <v>14.99</v>
@@ -1182,7 +1337,7 @@
         <v>4.83</v>
       </c>
       <c r="N13" t="n">
-        <v>5.01</v>
+        <v>6.74</v>
       </c>
       <c r="O13" t="n">
         <v>-3.63</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>14.3</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44526</v>
+        <v>44529</v>
       </c>
       <c r="H14" t="n">
-        <v>310.3</v>
+        <v>303.6</v>
       </c>
       <c r="I14" t="n">
         <v>305.5709207047276</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.69</v>
+        <v>-11.64</v>
       </c>
       <c r="L14" t="n">
-        <v>10.77</v>
+        <v>12.69</v>
       </c>
       <c r="M14" t="n">
         <v>1.26</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>14.38</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H15" t="n">
-        <v>284.6</v>
+        <v>302.7</v>
       </c>
       <c r="I15" t="n">
         <v>302.1136557249334</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K15" t="n">
-        <v>6.26</v>
+        <v>0.3</v>
       </c>
       <c r="L15" t="n">
         <v>6.49</v>
@@ -1296,7 +1475,7 @@
         <v>1.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.42</v>
+        <v>6.36</v>
       </c>
       <c r="O15" t="n">
         <v>-2.16</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.1</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H16" t="n">
-        <v>281.8</v>
+        <v>278.9</v>
       </c>
       <c r="I16" t="n">
         <v>281.1834388628039</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.9</v>
+        <v>-7.86</v>
       </c>
       <c r="L16" t="n">
         <v>9.15</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>9.23</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44607</v>
+        <v>44608</v>
       </c>
       <c r="H17" t="n">
-        <v>281.6</v>
+        <v>294.3</v>
       </c>
       <c r="I17" t="n">
         <v>292.870582044865</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.97</v>
+        <v>-5.52</v>
       </c>
       <c r="L17" t="n">
         <v>8.57</v>
@@ -1410,7 +1613,7 @@
         <v>2.44</v>
       </c>
       <c r="N17" t="n">
-        <v>1.59</v>
+        <v>4.51</v>
       </c>
       <c r="O17" t="n">
         <v>-1.03</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>12.84</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H18" t="n">
-        <v>274.6</v>
+        <v>253</v>
       </c>
       <c r="I18" t="n">
         <v>257.1932570083277</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.69</v>
+        <v>-14.03</v>
       </c>
       <c r="L18" t="n">
-        <v>17.02</v>
+        <v>19.47</v>
       </c>
       <c r="M18" t="n">
         <v>2.79</v>
       </c>
       <c r="N18" t="n">
-        <v>3.76</v>
+        <v>7.87</v>
       </c>
       <c r="O18" t="n">
         <v>4.51</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>18.33</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44631</v>
+        <v>44634</v>
       </c>
       <c r="H19" t="n">
-        <v>267.7</v>
+        <v>321.2</v>
       </c>
       <c r="I19" t="n">
         <v>299.3640691691526</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.81</v>
+        <v>-26.96</v>
       </c>
       <c r="L19" t="n">
-        <v>20</v>
+        <v>26.96</v>
       </c>
       <c r="M19" t="n">
-        <v>4.94</v>
+        <v>10.53</v>
       </c>
       <c r="N19" t="n">
-        <v>5.71</v>
+        <v>19.99</v>
       </c>
       <c r="O19" t="n">
         <v>-7.87</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>23.18</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44643</v>
+        <v>44644</v>
       </c>
       <c r="H20" t="n">
-        <v>299.2</v>
+        <v>290.9</v>
       </c>
       <c r="I20" t="n">
         <v>296.0180089129528</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.85</v>
+        <v>-9.43</v>
       </c>
       <c r="L20" t="n">
         <v>16.47</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>27.68</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44676</v>
+        <v>44677</v>
       </c>
       <c r="H21" t="n">
-        <v>316.6</v>
+        <v>345.3</v>
       </c>
       <c r="I21" t="n">
         <v>338.8337676769342</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.83</v>
+        <v>-18.7</v>
       </c>
       <c r="L21" t="n">
-        <v>15.64</v>
+        <v>20.28</v>
       </c>
       <c r="M21" t="n">
         <v>4.94</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>22.27</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H22" t="n">
-        <v>328.3</v>
+        <v>319.6</v>
       </c>
       <c r="I22" t="n">
         <v>320.4879716052507</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.92</v>
+        <v>-7.44</v>
       </c>
       <c r="L22" t="n">
         <v>15.06</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>16.54</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44770</v>
+        <v>44771</v>
       </c>
       <c r="H23" t="n">
-        <v>363.1</v>
+        <v>377.9</v>
       </c>
       <c r="I23" t="n">
         <v>372.4608642316093</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K23" t="n">
-        <v>-13.61</v>
+        <v>-18.24</v>
       </c>
       <c r="L23" t="n">
-        <v>15.83</v>
+        <v>19.31</v>
       </c>
       <c r="M23" t="n">
         <v>0.77</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.08</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44874</v>
+        <v>44875</v>
       </c>
       <c r="H24" t="n">
-        <v>449.4</v>
+        <v>431</v>
       </c>
       <c r="I24" t="n">
         <v>439.6675187032678</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K24" t="n">
-        <v>18.92</v>
+        <v>14.05</v>
       </c>
       <c r="L24" t="n">
         <v>6.06</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.31</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44991</v>
+        <v>44993</v>
       </c>
       <c r="H25" t="n">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="I25" t="n">
         <v>337.2891710929715</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K25" t="n">
-        <v>22.51</v>
+        <v>20.88</v>
       </c>
       <c r="L25" t="n">
         <v>4.25</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>12.65</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45001</v>
+        <v>45002</v>
       </c>
       <c r="H26" t="n">
-        <v>315.2</v>
+        <v>299.5</v>
       </c>
       <c r="I26" t="n">
         <v>300.2575979176621</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.57</v>
+        <v>-12.17</v>
       </c>
       <c r="L26" t="n">
-        <v>10.44</v>
+        <v>12.2</v>
       </c>
       <c r="M26" t="n">
         <v>4.51</v>
       </c>
       <c r="N26" t="n">
-        <v>3.01</v>
+        <v>4.98</v>
       </c>
       <c r="O26" t="n">
         <v>2.1</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>15.73</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45068</v>
+        <v>45069</v>
       </c>
       <c r="H27" t="n">
-        <v>315.8</v>
+        <v>331.3</v>
       </c>
       <c r="I27" t="n">
         <v>329.9072716385125</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.44</v>
+        <v>-10.62</v>
       </c>
       <c r="L27" t="n">
         <v>11.29</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>11.61</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45162</v>
+        <v>45163</v>
       </c>
       <c r="H28" t="n">
-        <v>419.8</v>
+        <v>418.9</v>
       </c>
       <c r="I28" t="n">
         <v>419.5878473524267</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="n">
-        <v>26.71</v>
+        <v>26.44</v>
       </c>
       <c r="L28" t="n">
         <v>5.77</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45210</v>
+        <v>45211</v>
       </c>
       <c r="H29" t="n">
-        <v>438.3</v>
+        <v>443.7</v>
       </c>
       <c r="I29" t="n">
         <v>441.3575617449012</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.63</v>
+        <v>-5.92</v>
       </c>
       <c r="L29" t="n">
         <v>7.42</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.16</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45358</v>
+        <v>45362</v>
       </c>
       <c r="H30" t="n">
-        <v>508.8</v>
+        <v>495.2</v>
       </c>
       <c r="I30" t="n">
         <v>506.4130428147313</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K30" t="n">
-        <v>14.67</v>
+        <v>11.61</v>
       </c>
       <c r="L30" t="n">
         <v>10.39</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.34</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45404</v>
+        <v>45405</v>
       </c>
       <c r="H31" t="n">
-        <v>488.8</v>
+        <v>495.9</v>
       </c>
       <c r="I31" t="n">
         <v>490.0167550791351</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K31" t="n">
-        <v>1.29</v>
+        <v>-0.14</v>
       </c>
       <c r="L31" t="n">
         <v>3.8</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>11.2</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H32" t="n">
-        <v>470.2</v>
+        <v>451.1</v>
       </c>
       <c r="I32" t="n">
         <v>469.3736031886982</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.18</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>5.97</v>
+        <v>9.92</v>
       </c>
       <c r="M32" t="n">
         <v>4.07</v>
       </c>
       <c r="N32" t="n">
-        <v>3.93</v>
+        <v>4.06</v>
       </c>
       <c r="O32" t="n">
         <v>1.45</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.85</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45467</v>
+        <v>45468</v>
       </c>
       <c r="H33" t="n">
-        <v>486.6</v>
+        <v>509.5</v>
       </c>
       <c r="I33" t="n">
         <v>506.9185321770012</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.87</v>
+        <v>-12.95</v>
       </c>
       <c r="L33" t="n">
-        <v>11.95</v>
+        <v>15.05</v>
       </c>
       <c r="M33" t="n">
         <v>7.69</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.45</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="H34" t="n">
-        <v>603</v>
+        <v>583</v>
       </c>
       <c r="I34" t="n">
         <v>600.0194857257321</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K34" t="n">
-        <v>18.35</v>
+        <v>14.43</v>
       </c>
       <c r="L34" t="n">
         <v>6.3</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.71</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45580</v>
+        <v>45581</v>
       </c>
       <c r="H35" t="n">
-        <v>576.7</v>
+        <v>588.2</v>
       </c>
       <c r="I35" t="n">
         <v>585.5012955138525</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K35" t="n">
-        <v>1.08</v>
+        <v>-0.89</v>
       </c>
       <c r="L35" t="n">
         <v>4.03</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.5</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45650</v>
+        <v>45652</v>
       </c>
       <c r="H36" t="n">
-        <v>578.8</v>
+        <v>573.4</v>
       </c>
       <c r="I36" t="n">
         <v>574.7318930254227</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.6</v>
+        <v>-2.52</v>
       </c>
       <c r="L36" t="n">
         <v>7.17</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.76</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45749</v>
+        <v>45750</v>
       </c>
       <c r="H37" t="n">
-        <v>608.2</v>
+        <v>626.2</v>
       </c>
       <c r="I37" t="n">
         <v>623.6050915958443</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.07</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L37" t="n">
         <v>10.8</v>
@@ -2550,7 +2993,7 @@
         <v>1.28</v>
       </c>
       <c r="N37" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="O37" t="n">
         <v>-0.93</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="H38" t="n">
-        <v>611</v>
+        <v>599.7</v>
       </c>
       <c r="I38" t="n">
         <v>608.9679692838394</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.43</v>
+        <v>-4.23</v>
       </c>
       <c r="L38" t="n">
         <v>7.3</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45852</v>
+        <v>45853</v>
       </c>
       <c r="H39" t="n">
-        <v>557.9</v>
+        <v>581.5</v>
       </c>
       <c r="I39" t="n">
         <v>576.2428163140772</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K39" t="n">
-        <v>6.97</v>
+        <v>3.03</v>
       </c>
       <c r="L39" t="n">
         <v>3.03</v>
@@ -2664,7 +3131,7 @@
         <v>1.43</v>
       </c>
       <c r="N39" t="n">
-        <v>3.36</v>
+        <v>4.23</v>
       </c>
       <c r="O39" t="n">
         <v>-1.85</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="H40" t="n">
-        <v>606.8</v>
+        <v>601.6</v>
       </c>
       <c r="I40" t="n">
         <v>603.4580860036041</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>4.35</v>
+        <v>3.46</v>
       </c>
       <c r="L40" t="n">
         <v>4.16</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H41" t="n">
-        <v>557</v>
+        <v>572.95</v>
       </c>
       <c r="I41" t="n">
         <v>572.561686719049</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K41" t="n">
-        <v>7.41</v>
+        <v>4.76</v>
       </c>
       <c r="L41" t="n">
         <v>2.23</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>6</v>
+      </c>
+      <c r="U41" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.58</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="H42" t="n">
-        <v>543.55</v>
+        <v>521.6</v>
       </c>
       <c r="I42" t="n">
         <v>536.5800487907607</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.13</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>5.57</v>
+        <v>9.59</v>
       </c>
       <c r="M42" t="n">
         <v>0.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.27</v>
+        <v>4.04</v>
       </c>
       <c r="O42" t="n">
         <v>2.86</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.22</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="H43" t="n">
-        <v>530.2</v>
+        <v>538.25</v>
       </c>
       <c r="I43" t="n">
         <v>536.6208838478273</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.65</v>
+        <v>-3.19</v>
       </c>
       <c r="L43" t="n">
         <v>4.48</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H44" t="n">
-        <v>490.6</v>
+        <v>481.6</v>
       </c>
       <c r="I44" t="n">
         <v>487.7349198297464</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K44" t="n">
-        <v>-8.85</v>
+        <v>-10.52</v>
       </c>
       <c r="L44" t="n">
-        <v>10.07</v>
+        <v>10.81</v>
       </c>
       <c r="M44" t="n">
         <v>1.57</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="H45" t="n">
-        <v>338.55</v>
+        <v>365</v>
       </c>
       <c r="I45" t="n">
         <v>356.1931341221041</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K45" t="n">
-        <v>29.7</v>
+        <v>24.21</v>
       </c>
       <c r="L45" t="n">
         <v>2.67</v>
@@ -3006,7 +3545,7 @@
         <v>3.06</v>
       </c>
       <c r="N45" t="n">
-        <v>4.14</v>
+        <v>7.81</v>
       </c>
       <c r="O45" t="n">
         <v>-1.83</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>7</v>
+      </c>
+      <c r="U45" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.31</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H46" t="n">
-        <v>371.4</v>
+        <v>363</v>
       </c>
       <c r="I46" t="n">
         <v>370.9437300995219</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K46" t="n">
-        <v>1.75</v>
+        <v>-0.55</v>
       </c>
       <c r="L46" t="n">
         <v>7.53</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3123,6 +3686,14 @@
       <c r="Q47" t="n">
         <v>19</v>
       </c>
+      <c r="R47" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6041,7 +6612,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.6</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="6">
@@ -6051,7 +6622,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -6061,7 +6632,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8">
@@ -6071,7 +6642,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -6081,7 +6652,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -6091,7 +6662,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>110.8</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="11">
@@ -6131,7 +6702,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53.74</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="15">
@@ -6141,7 +6712,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101.17</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="16">
@@ -6151,7 +6722,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.15</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="17">
@@ -6161,7 +6732,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2115.62</v>
+        <v>2005.21</v>
       </c>
     </row>
     <row r="18">
@@ -6171,7 +6742,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6181,7 +6752,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.43</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -6191,7 +6762,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.49</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="21">
@@ -6201,7 +6772,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="22">
@@ -6221,7 +6792,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -6231,7 +6802,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.37</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="25">
@@ -6251,7 +6822,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.78</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="27">
@@ -6261,7 +6832,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15.84</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="28">
@@ -6271,7 +6842,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
